--- a/test_cases/test_cases.xlsx
+++ b/test_cases/test_cases.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
